--- a/data/trans_dic/IP07_C11_R_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP07_C11_R_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,239 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que tienen muchos o muchísimos problemas para dormir, percibido por el menor (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>8,49%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4,64%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6,87%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>4,2; 15,17</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1,27; 10,19</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4,08; 11,7</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>7,55%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>0,52; 4,9</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4,01; 14,17</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2,42; 7,26</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>4,29%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>6,49%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>5,22%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>2,33; 7,0</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>3,69; 10,74</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>3,65; 7,77</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A6:A7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -777,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.08488388897646885</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.04638947045791559</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.06868154491023964</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>8363</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>3322</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>11684</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.04201081117577071</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.0127365990883385</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.04084166189482667</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>4139; 14944</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>912; 7299</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6948; 19907</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.1516875599317554</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.1019300919301087</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.1170154297087281</v>
       </c>
     </row>
     <row r="7">
@@ -850,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.01882451216961452</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.07547839923649084</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.04281062596781945</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>3230</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>9509</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>12739</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.005154187726302647</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.0401288095880792</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.02423244351070214</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>884; 8415</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>5056; 17846</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>7211; 21591</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.04904602520213838</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.1416584200739472</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.0725585356002605</v>
       </c>
     </row>
     <row r="10">
@@ -923,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.04291972559507507</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.0649365817223452</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.05222136713447853</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>11593</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>12831</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>24423</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.02334315025834651</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.03687671746223254</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.03645664564330427</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>6305; 18901</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>7286; 21217</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>17050; 36334</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.06997729522484769</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.1073820666162268</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.077689330318472</v>
       </c>
     </row>
     <row r="13">
@@ -1004,4 +725,303 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que tienen muchos o muchísimos problemas para dormir, percibido por el menor (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>8363</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>3322</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>11684</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>4139</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>912</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>6948</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>14944</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>7299</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>19907</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>3230</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>9509</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>12739</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>884</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>5056</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>7211</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>8415</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>17846</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>21591</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>11593</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>12831</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>24423</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>6305</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>7286</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>17050</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>18901</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>21217</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>36334</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A12:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>